--- a/leetcode qsn.xlsx
+++ b/leetcode qsn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEAD7E2-DAAF-453F-9DEB-F4DE469E622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168903B2-3630-4C6D-ABFF-B860F12150DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARRAYS" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="362">
   <si>
     <t>Arrays Easy</t>
   </si>
@@ -1111,6 +1111,12 @@
   </si>
   <si>
     <t>done //</t>
+  </si>
+  <si>
+    <t>done/</t>
+  </si>
+  <si>
+    <t>done//</t>
   </si>
 </sst>
 </file>
@@ -3069,6 +3075,9 @@
       <c r="A2" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="D2" t="s">
+        <v>360</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
@@ -3081,7 +3090,7 @@
         <v>78</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>4</v>
+        <v>361</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>79</v>
@@ -3605,15 +3614,11 @@
       <c r="A2" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="3" t="s">
         <v>176</v>
       </c>
@@ -3622,9 +3627,7 @@
       <c r="A3" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="3" t="s">
         <v>178</v>
       </c>
@@ -3636,15 +3639,11 @@
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L4" s="4"/>
       <c r="M4" s="7" t="s">
         <v>182</v>
       </c>
@@ -3653,9 +3652,7 @@
       <c r="A5" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="3" t="s">
         <v>184</v>
       </c>
@@ -3667,15 +3664,11 @@
       <c r="A6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F6" s="4"/>
       <c r="G6" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L6" s="4"/>
       <c r="M6" s="8" t="s">
         <v>188</v>
       </c>
@@ -3684,15 +3677,11 @@
       <c r="A7" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L7" s="4"/>
       <c r="M7" s="8" t="s">
         <v>191</v>
       </c>
@@ -3715,9 +3704,7 @@
       <c r="G9" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L9" s="4"/>
       <c r="M9" s="8" t="s">
         <v>197</v>
       </c>
@@ -3734,9 +3721,7 @@
       <c r="A11" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="3" t="s">
         <v>201</v>
       </c>
@@ -3762,9 +3747,7 @@
       <c r="G13" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L13" s="4"/>
       <c r="M13" s="8" t="s">
         <v>208</v>
       </c>
@@ -3773,15 +3756,11 @@
       <c r="A14" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F14" s="4"/>
       <c r="G14" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L14" s="4"/>
       <c r="M14" s="8" t="s">
         <v>211</v>
       </c>
@@ -3790,15 +3769,11 @@
       <c r="A15" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="L15" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L15" s="4"/>
       <c r="M15" s="8" t="s">
         <v>214</v>
       </c>
@@ -3818,9 +3793,7 @@
       <c r="A17" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F17" s="4"/>
       <c r="G17" s="3" t="s">
         <v>219</v>
       </c>
@@ -3829,9 +3802,7 @@
       <c r="G18" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
         <v>221</v>
       </c>

--- a/leetcode qsn.xlsx
+++ b/leetcode qsn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168903B2-3630-4C6D-ABFF-B860F12150DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0766F9CA-632A-4171-B064-2150E637FF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARRAYS" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="363">
   <si>
     <t>Arrays Easy</t>
   </si>
@@ -1117,6 +1117,9 @@
   </si>
   <si>
     <t>done//</t>
+  </si>
+  <si>
+    <t>bullshit ass qsn/</t>
   </si>
 </sst>
 </file>
@@ -3103,6 +3106,9 @@
       <c r="A4" s="3" t="s">
         <v>81</v>
       </c>
+      <c r="D4" t="s">
+        <v>362</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>82</v>
       </c>
@@ -3113,6 +3119,9 @@
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>84</v>
+      </c>
+      <c r="D5" t="s">
+        <v>359</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>85</v>
@@ -3417,10 +3426,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>139</v>
       </c>
@@ -3428,7 +3437,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>141</v>
       </c>
@@ -3436,7 +3445,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>143</v>
       </c>
@@ -3444,7 +3453,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>145</v>
       </c>
@@ -3452,7 +3461,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>147</v>
       </c>
@@ -3460,7 +3469,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>149</v>
       </c>
@@ -3468,7 +3477,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>151</v>
       </c>
@@ -3476,7 +3485,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>153</v>
       </c>
@@ -3484,25 +3493,28 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>155</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F11" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
@@ -3510,7 +3522,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>161</v>
       </c>
@@ -3518,7 +3530,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>163</v>
       </c>
@@ -3526,12 +3538,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>166</v>
       </c>
@@ -3909,9 +3921,7 @@
         <v>229</v>
       </c>
       <c r="B2" s="6"/>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="8" t="s">
         <v>230</v>
       </c>
@@ -3921,9 +3931,7 @@
         <v>231</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="F3" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="8" t="s">
         <v>232</v>
       </c>
@@ -3933,9 +3941,7 @@
         <v>233</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="F4" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="8" t="s">
         <v>234</v>
       </c>
@@ -3945,9 +3951,7 @@
         <v>235</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="F5" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="8" t="s">
         <v>236</v>
       </c>
@@ -3977,9 +3981,7 @@
         <v>241</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="F9" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="8" t="s">
         <v>242</v>
       </c>
@@ -3989,9 +3991,7 @@
         <v>243</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="F10" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="8" t="s">
         <v>244</v>
       </c>
@@ -4008,9 +4008,7 @@
         <v>246</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="F12" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F12" s="4"/>
       <c r="G12" s="8" t="s">
         <v>247</v>
       </c>
@@ -4020,9 +4018,7 @@
         <v>248</v>
       </c>
       <c r="B13" s="6"/>
-      <c r="F13" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="8" t="s">
         <v>249</v>
       </c>
@@ -4032,9 +4028,7 @@
         <v>250</v>
       </c>
       <c r="B14" s="6"/>
-      <c r="F14" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F14" s="4"/>
       <c r="G14" s="8" t="s">
         <v>251</v>
       </c>
@@ -4044,9 +4038,7 @@
         <v>252</v>
       </c>
       <c r="B15" s="6"/>
-      <c r="F15" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="8" t="s">
         <v>253</v>
       </c>

--- a/leetcode qsn.xlsx
+++ b/leetcode qsn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0766F9CA-632A-4171-B064-2150E637FF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEB1550-F22F-4F70-9F2E-5E32F56C0503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARRAYS" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="361">
   <si>
     <t>Arrays Easy</t>
   </si>
@@ -45,9 +45,6 @@
     <t>https://leetcode.com/problems/two-sum/</t>
   </si>
   <si>
-    <t>done</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/merge-intervals/</t>
   </si>
   <si>
@@ -931,9 +928,6 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/reverse-linked-list</t>
-  </si>
-  <si>
-    <t>dne</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/add-two-numbers/</t>
@@ -1498,208 +1492,208 @@
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="T2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q3" s="4"/>
       <c r="T3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="T4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>356</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>358</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="I11" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q15" s="4"/>
     </row>
     <row r="16" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="10:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="10:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J18" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="10:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J19" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="10:17" ht="14.4" x14ac:dyDescent="0.3">
       <c r="J20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="10:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="10:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="10:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q23" s="4"/>
     </row>
     <row r="24" spans="10:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q24" s="4"/>
     </row>
     <row r="25" spans="10:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J25" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="10:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J26" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q26" s="4"/>
     </row>
@@ -2679,27 +2673,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -2723,118 +2717,118 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F10" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F14" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F15" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F16" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2879,22 +2873,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -2916,114 +2910,104 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3065,164 +3049,164 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D4" t="s">
-        <v>362</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E14" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3277,117 +3261,117 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F8" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F10" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K11" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K12" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K13" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K14" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3431,141 +3415,144 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>144</v>
+      <c r="J3" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J9" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F11" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3613,233 +3600,233 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>184</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="M8" s="8" t="s">
         <v>193</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="M12" s="7" t="s">
         <v>204</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="M16" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G18" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G19" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M19" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M20" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M21" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M22" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3910,217 +3897,227 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B2" s="6"/>
       <c r="F2" s="4"/>
       <c r="G2" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="F3" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>231</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="8" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="F4" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="8" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="F5" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="8" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="G6" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B8" s="6"/>
       <c r="G8" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B9" s="6"/>
       <c r="F9" s="4"/>
       <c r="G9" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B10" s="6"/>
       <c r="F10" s="4"/>
       <c r="G10" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="6"/>
       <c r="G11" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="F12" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="8" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="F13" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="8" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B14" s="6"/>
       <c r="F14" s="4"/>
       <c r="G14" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B15" s="6"/>
       <c r="F15" s="4"/>
       <c r="G15" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="6"/>
       <c r="G17" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B18" s="6"/>
       <c r="G18" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B19" s="6"/>
       <c r="G19" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B20" s="6"/>
       <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B21" s="6"/>
       <c r="G21" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B22" s="6"/>
       <c r="G22" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" s="6"/>
       <c r="G23" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="6"/>
       <c r="G24" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="6"/>
       <c r="G25" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="G26" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
@@ -4518,125 +4515,117 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>274</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="K7" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>290</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F14" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F15" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F16" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4679,158 +4668,126 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="F6" s="4"/>
       <c r="G6" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G12" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G13" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G14" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>4</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G15" s="11" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/leetcode qsn.xlsx
+++ b/leetcode qsn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEB1550-F22F-4F70-9F2E-5E32F56C0503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74E93F4-7A52-4B77-BAF0-9649BAFFA95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARRAYS" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="GREEDY, DFS" sheetId="5" r:id="rId5"/>
     <sheet name="TREE, BFS" sheetId="6" r:id="rId6"/>
     <sheet name="BINARY SEARCH, HEAPS" sheetId="7" r:id="rId7"/>
-    <sheet name="BACKTRACKING, STACK" sheetId="8" r:id="rId8"/>
-    <sheet name="LINKED LIST" sheetId="9" r:id="rId9"/>
+    <sheet name="LINKED LIST" sheetId="9" r:id="rId8"/>
+    <sheet name="BACKTRACKING, STACK" sheetId="8" r:id="rId9"/>
     <sheet name="SLIDING WINDOW" sheetId="10" r:id="rId10"/>
     <sheet name="DESIGN, GRAPH" sheetId="11" r:id="rId11"/>
     <sheet name="TRIE, SEGMENT TREE" sheetId="12" r:id="rId12"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="361">
   <si>
     <t>Arrays Easy</t>
   </si>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B4" s="6"/>
       <c r="F4" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>233</v>
@@ -3974,7 +3974,9 @@
         <v>240</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>358</v>
+      </c>
       <c r="G9" s="8" t="s">
         <v>241</v>
       </c>
@@ -4014,7 +4016,7 @@
       </c>
       <c r="B13" s="6"/>
       <c r="F13" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>248</v>
@@ -4506,159 +4508,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F14" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F15" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F16" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
-    <hyperlink ref="A4" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
-    <hyperlink ref="F4" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
-    <hyperlink ref="A5" r:id="rId7" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
-    <hyperlink ref="F5" r:id="rId8" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
-    <hyperlink ref="A6" r:id="rId9" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
-    <hyperlink ref="F6" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
-    <hyperlink ref="A7" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
-    <hyperlink ref="F7" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
-    <hyperlink ref="A10" r:id="rId13" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
-    <hyperlink ref="F10" r:id="rId14" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
-    <hyperlink ref="A11" r:id="rId15" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
-    <hyperlink ref="F11" r:id="rId16" xr:uid="{00000000-0004-0000-0700-00000F000000}"/>
-    <hyperlink ref="A12" r:id="rId17" xr:uid="{00000000-0004-0000-0700-000010000000}"/>
-    <hyperlink ref="F12" r:id="rId18" xr:uid="{00000000-0004-0000-0700-000011000000}"/>
-    <hyperlink ref="A13" r:id="rId19" xr:uid="{00000000-0004-0000-0700-000012000000}"/>
-    <hyperlink ref="F13" r:id="rId20" xr:uid="{00000000-0004-0000-0700-000013000000}"/>
-    <hyperlink ref="F14" r:id="rId21" xr:uid="{00000000-0004-0000-0700-000014000000}"/>
-    <hyperlink ref="F15" r:id="rId22" xr:uid="{00000000-0004-0000-0700-000015000000}"/>
-    <hyperlink ref="F16" r:id="rId23" xr:uid="{00000000-0004-0000-0700-000016000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4819,4 +4668,157 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F14" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" s="8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F16" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
+    <hyperlink ref="F4" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
+    <hyperlink ref="A5" r:id="rId7" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
+    <hyperlink ref="F5" r:id="rId8" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
+    <hyperlink ref="A6" r:id="rId9" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="F6" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
+    <hyperlink ref="A7" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
+    <hyperlink ref="F7" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
+    <hyperlink ref="A10" r:id="rId13" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
+    <hyperlink ref="F10" r:id="rId14" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
+    <hyperlink ref="A11" r:id="rId15" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
+    <hyperlink ref="F11" r:id="rId16" xr:uid="{00000000-0004-0000-0700-00000F000000}"/>
+    <hyperlink ref="A12" r:id="rId17" xr:uid="{00000000-0004-0000-0700-000010000000}"/>
+    <hyperlink ref="F12" r:id="rId18" xr:uid="{00000000-0004-0000-0700-000011000000}"/>
+    <hyperlink ref="A13" r:id="rId19" xr:uid="{00000000-0004-0000-0700-000012000000}"/>
+    <hyperlink ref="F13" r:id="rId20" xr:uid="{00000000-0004-0000-0700-000013000000}"/>
+    <hyperlink ref="F14" r:id="rId21" xr:uid="{00000000-0004-0000-0700-000014000000}"/>
+    <hyperlink ref="F15" r:id="rId22" xr:uid="{00000000-0004-0000-0700-000015000000}"/>
+    <hyperlink ref="F16" r:id="rId23" xr:uid="{00000000-0004-0000-0700-000016000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>